--- a/output/pdf_financials_xlsx/ELF.xlsx
+++ b/output/pdf_financials_xlsx/ELF.xlsx
@@ -56037,7 +56037,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
